--- a/data/output/restoration_brazil.xlsx
+++ b/data/output/restoration_brazil.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
     <t xml:space="preserve">iso3</t>
   </si>
@@ -108,6 +108,18 @@
   </si>
   <si>
     <t xml:space="preserve">Williams et al. (2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">restoration_pasture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barrios et al. (2023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restoration potential of moderate and severely degraded pasture</t>
   </si>
 </sst>
 </file>
@@ -616,6 +628,26 @@
         <v>10</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="n">
+        <v>80.87</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
